--- a/output/full_scan/batch_seq8_2026-09-03.xlsx
+++ b/output/full_scan/batch_seq8_2026-09-03.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O128"/>
+  <dimension ref="A1:O129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6906</v>
+        <v>6933</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>722.2825589588283</v>
+        <v>807.8042025641819</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>302</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>65.63188828273169</v>
+        <v>73.98319315153937</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>26.60817627045314</v>
+        <v>38.39502378379896</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5.35975943912269</v>
+        <v>1.380420256418189</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.216126491884126</v>
+        <v>12.48647089078323</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6918</v>
+        <v>6906</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>719.3261336056145</v>
+        <v>722.2825589588283</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>61.3124026406424</v>
+        <v>65.63188828273169</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>38.75557320804697</v>
+        <v>26.60817627045314</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.5406310249787452</v>
+        <v>5.35975943912269</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.2729126767410825</v>
+        <v>1.216126491884126</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7730</v>
+        <v>6918</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>703.0801415326544</v>
+        <v>719.3261336056145</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>188</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>60.84721047192617</v>
+        <v>61.3124026406424</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>15.79771989414224</v>
+        <v>38.75557320804697</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.083651182930814</v>
+        <v>0.5406310249787452</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.493155283464005</v>
+        <v>0.2729126767410825</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6922</v>
+        <v>7730</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>691.5578758944035</v>
+        <v>703.0801415326544</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>52.35910114422396</v>
+        <v>60.84721047192617</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>27.24042949459352</v>
+        <v>15.79771989414224</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.518863977463218</v>
+        <v>3.083651182930814</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.5773788417469685</v>
+        <v>1.493155283464005</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7810</v>
+        <v>6922</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>690.7587134469186</v>
+        <v>691.5578758944035</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>218.5</v>
+        <v>201</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>61.49027805463791</v>
+        <v>52.35910114422396</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>35.80984885847002</v>
+        <v>27.24042949459352</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.9234317863488096</v>
+        <v>0.518863977463218</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>1.731539106000275</v>
+        <v>-0.5773788417469685</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6840</v>
+        <v>7810</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>681.2500227317031</v>
+        <v>690.7587134469186</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>218.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>66.22612685783646</v>
+        <v>61.49027805463791</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>39.79817811128176</v>
+        <v>35.80984885847002</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.7754969744856542</v>
+        <v>0.9234317863488096</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.3443778278762499</v>
+        <v>1.731539106000275</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7772</v>
+        <v>6840</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>675.4388315805176</v>
+        <v>681.2500227317031</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>99.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>58.14820718546565</v>
+        <v>66.22612685783646</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15.4457664759733</v>
+        <v>39.79817811128176</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.730650572720959</v>
+        <v>0.7754969744856542</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1.879117383495635</v>
+        <v>0.3443778278762499</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7744</v>
+        <v>7772</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>664.3094598753123</v>
+        <v>675.4388315805176</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>521</v>
+        <v>99.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.26095141667369</v>
+        <v>58.14820718546565</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>34.98597607122746</v>
+        <v>15.4457664759733</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.8792527688471273</v>
+        <v>3.730650572720959</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>2.845507849434025</v>
+        <v>1.879117383495635</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6838</v>
+        <v>7744</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>636.450249413665</v>
+        <v>664.3094598753123</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>24</v>
+        <v>521</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.6697743986692</v>
+        <v>60.26095141667369</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15.26800746012946</v>
+        <v>34.98597607122746</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.64282027739564</v>
+        <v>0.8792527688471273</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.131340332077777</v>
+        <v>2.845507849434025</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6913</v>
+        <v>6838</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>608.220114135898</v>
+        <v>636.450249413665</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>149</v>
+        <v>24</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>54.45983466277925</v>
+        <v>60.6697743986692</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>28.98119895724665</v>
+        <v>15.26800746012946</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.7039477147979294</v>
+        <v>3.64282027739564</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.286760448275726</v>
+        <v>0.131340332077777</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7792</v>
+        <v>6913</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>607.1542351848794</v>
+        <v>608.220114135898</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>305</v>
+        <v>149</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>68.52391409610338</v>
+        <v>54.45983466277925</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>51.07208969221969</v>
+        <v>28.98119895724665</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.3259001894628459</v>
+        <v>0.7039477147979294</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>2.442995311115411</v>
+        <v>0.286760448275726</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7788</v>
+        <v>7792</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>587.496265461675</v>
+        <v>607.1542351848794</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>66.53694449071118</v>
+        <v>68.52391409610338</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>33.03386998950686</v>
+        <v>51.07208969221969</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.524961282712153</v>
+        <v>0.3259001894628459</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>5.246508555031586</v>
+        <v>2.442995311115411</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7711</v>
+        <v>7788</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>584.919599583726</v>
+        <v>587.496265461675</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>575</v>
+        <v>315</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>70.03545598461741</v>
+        <v>66.53694449071118</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>48.29733741383126</v>
+        <v>33.03386998950686</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.044119853010772</v>
+        <v>1.524961282712153</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>8.039685346173577</v>
+        <v>5.246508555031586</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7610</v>
+        <v>7711</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>552.6097709756979</v>
+        <v>584.919599583726</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1655</v>
+        <v>575</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>49.18140085138964</v>
+        <v>70.03545598461741</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>12.22372749924699</v>
+        <v>48.29733741383126</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.976687153723794</v>
+        <v>1.044119853010772</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>2.122239331316728</v>
+        <v>8.039685346173577</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7728</v>
+        <v>7610</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>532.5240553884503</v>
+        <v>552.6097709756979</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>639</v>
+        <v>1655</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.41219450538728</v>
+        <v>49.18140085138964</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>22.57011968846163</v>
+        <v>12.22372749924699</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.661591703817638</v>
+        <v>1.976687153723794</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>9.009959090209056</v>
+        <v>2.122239331316728</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7712</v>
+        <v>7728</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>530.5498487630821</v>
+        <v>532.5240553884503</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>152</v>
+        <v>639</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>51.64607217188486</v>
+        <v>55.41219450538728</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18.99354340327443</v>
+        <v>22.57011968846163</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.8779553996789611</v>
+        <v>1.661591703817638</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.317684422233498</v>
+        <v>9.009959090209056</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6870</v>
+        <v>7712</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>528.4875933302576</v>
+        <v>530.5498487630821</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>62.25707367367449</v>
+        <v>51.64607217188486</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>13.30955104733933</v>
+        <v>18.99354340327443</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.495525362620428</v>
+        <v>0.8779553996789611</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>3.876206285158356</v>
+        <v>1.317684422233498</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6953</v>
+        <v>6870</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>508.9634276640823</v>
+        <v>528.4875933302576</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>237.5</v>
+        <v>288</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.63144631922791</v>
+        <v>62.25707367367449</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>19.57986076803402</v>
+        <v>13.30955104733933</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.3406038498998133</v>
+        <v>1.495525362620428</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.495209498388893</v>
+        <v>3.876206285158356</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>7769</v>
+        <v>6953</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>504.6944944947862</v>
+        <v>508.9634276640823</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>5870</v>
+        <v>237.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>41.76050053721858</v>
+        <v>55.63144631922791</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>10.42349856235495</v>
+        <v>19.57986076803402</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.515439712666224</v>
+        <v>0.3406038498998133</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-69.14785421016617</v>
+        <v>1.495209498388893</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6969</v>
+        <v>7769</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>501.7376694819059</v>
+        <v>504.6944944947862</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>33.35</v>
+        <v>5870</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>50.5814811330428</v>
+        <v>41.76050053721858</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>21.9808750667022</v>
+        <v>10.42349856235495</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5145476085856198</v>
+        <v>1.515439712666224</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.2259895148054531</v>
+        <v>-69.14785421016617</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8021</v>
+        <v>6969</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>499.9459729862704</v>
+        <v>501.7376694819059</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>413.5</v>
+        <v>33.35</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>47.95517431138309</v>
+        <v>50.5814811330428</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>11.71847940184239</v>
+        <v>21.9808750667022</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.413463514326144</v>
+        <v>0.5145476085856198</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>4.833290274014909</v>
+        <v>-0.2259895148054531</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6907</v>
+        <v>8021</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>492.6647620110274</v>
+        <v>499.9459729862704</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>177.5</v>
+        <v>413.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46.35756117841554</v>
+        <v>47.95517431138309</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>14.97013547795842</v>
+        <v>11.71847940184239</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6628049736704588</v>
+        <v>2.413463514326144</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.467228169361914</v>
+        <v>4.833290274014909</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6895</v>
+        <v>6907</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>486.8124411356661</v>
+        <v>492.6647620110274</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>153</v>
+        <v>177.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>62.97820649967797</v>
+        <v>46.35756117841554</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>31.18138714982673</v>
+        <v>14.97013547795842</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.338652569825781</v>
+        <v>0.6628049736704588</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>3.890151935817498</v>
+        <v>-0.467228169361914</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6936</v>
+        <v>6895</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>476.0017799555283</v>
+        <v>486.8124411356661</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>32.8</v>
+        <v>153</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.85879766596983</v>
+        <v>62.97820649967797</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>35.99714379471913</v>
+        <v>31.18138714982673</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8841891460823863</v>
+        <v>1.338652569825781</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0530403803634674</v>
+        <v>3.890151935817498</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6885</v>
+        <v>6936</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>466.8958421525826</v>
+        <v>476.0017799555283</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>23.25</v>
+        <v>32.8</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>61.6068029235181</v>
+        <v>56.85879766596983</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>35.5585729293657</v>
+        <v>35.99714379471913</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.314406053718653</v>
+        <v>0.8841891460823863</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.3428399657051617</v>
+        <v>0.0530403803634674</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2011,21 +2011,21 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6996</v>
+        <v>6885</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>466.5467266211455</v>
+        <v>466.8958421525826</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>183</v>
+        <v>23.25</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>54.99755349831605</v>
+        <v>61.6068029235181</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>12.30281014025794</v>
+        <v>35.5585729293657</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.659554680234148</v>
+        <v>1.314406053718653</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.7148991290321851</v>
+        <v>0.3428399657051617</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7556</v>
+        <v>6996</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>466.3958214798048</v>
+        <v>466.5467266211455</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>245</v>
+        <v>183</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>50.49818527406534</v>
+        <v>54.99755349831605</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>27.71576872120842</v>
+        <v>12.30281014025794</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8365536952656077</v>
+        <v>1.659554680234148</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.573875107436872</v>
+        <v>0.7148991290321851</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7402</v>
+        <v>7556</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>459.0109067402853</v>
+        <v>466.3958214798048</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>103</v>
+        <v>245</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>43.12363623771291</v>
+        <v>50.49818527406534</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>20.27812312662137</v>
+        <v>27.71576872120842</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5109382445739363</v>
+        <v>0.8365536952656077</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.2355512276993147</v>
+        <v>0.573875107436872</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6861</v>
+        <v>7402</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>454.0044262149121</v>
+        <v>459.0109067402853</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>178.5</v>
+        <v>103</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>33.89588320151215</v>
+        <v>43.12363623771291</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23.04026787745132</v>
+        <v>20.27812312662137</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.789771802173072</v>
+        <v>0.5109382445739363</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.379121117274213</v>
+        <v>-0.2355512276993147</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6937</v>
+        <v>6861</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>451.6854201555091</v>
+        <v>454.0044262149121</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>278</v>
+        <v>178.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>51.31360657488343</v>
+        <v>33.89588320151215</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>12.17858968046078</v>
+        <v>23.04026787745132</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.12171413243155</v>
+        <v>1.789771802173072</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.671015850747005</v>
+        <v>1.379121117274213</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8039</v>
+        <v>6937</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>451.2062877873647</v>
+        <v>451.6854201555091</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>55.87760185641614</v>
+        <v>51.31360657488343</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>37.41187272660378</v>
+        <v>12.17858968046078</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.020628778736466</v>
+        <v>1.12171413243155</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.8122954615682119</v>
+        <v>1.671015850747005</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>7631</v>
+        <v>8039</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>446.2857988001351</v>
+        <v>451.2062877873647</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>141</v>
+        <v>293</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>46.95787707401648</v>
+        <v>55.87760185641614</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24.64372193552481</v>
+        <v>37.41187272660378</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3256827558698515</v>
+        <v>1.020628778736466</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.2947854036720057</v>
+        <v>-0.8122954615682119</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6877</v>
+        <v>7631</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>445.2177824827708</v>
+        <v>446.2857988001351</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>36.82975737986619</v>
+        <v>46.95787707401648</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21.9045038365667</v>
+        <v>24.64372193552481</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.992350016380044</v>
+        <v>0.3256827558698515</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.4331224182932809</v>
+        <v>-0.2947854036720057</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6859</v>
+        <v>6877</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>442.9778021322912</v>
+        <v>445.2177824827708</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.81299843824321</v>
+        <v>36.82975737986619</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>23.71000211866439</v>
+        <v>21.9045038365667</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.014462521368504</v>
+        <v>1.992350016380044</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.7559697460258035</v>
+        <v>-0.4331224182932809</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6983</v>
+        <v>6859</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>441.6485781999148</v>
+        <v>442.9778021322912</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>358</v>
+        <v>112</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>64.62243319865084</v>
+        <v>56.81299843824321</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.94652002800635</v>
+        <v>23.71000211866439</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.264857819991481</v>
+        <v>1.014462521368504</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>7.758455189417408</v>
+        <v>0.7559697460258035</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>7750</v>
+        <v>6983</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>439.1729770583343</v>
+        <v>441.6485781999148</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2200</v>
+        <v>358</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>46.05373253945995</v>
+        <v>64.62243319865084</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12.66809746007339</v>
+        <v>20.94652002800635</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4423521034853097</v>
+        <v>1.264857819991481</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-23.65397687723165</v>
+        <v>7.758455189417408</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7818</v>
+        <v>7750</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>435.1268252620453</v>
+        <v>439.1729770583343</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>60.8</v>
+        <v>2200</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>34.66924451189132</v>
+        <v>46.05373253945995</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>19.49604375397911</v>
+        <v>12.66809746007339</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.222509298390057</v>
+        <v>0.4423521034853097</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0203664743521803</v>
+        <v>-23.65397687723165</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>7714</v>
+        <v>7818</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>430.1086551716622</v>
+        <v>435.1268252620453</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>160</v>
+        <v>60.8</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>46.24493016167287</v>
+        <v>34.66924451189132</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>23.3348851922939</v>
+        <v>19.49604375397911</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.6152613801573152</v>
+        <v>1.222509298390057</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.320717953998337</v>
+        <v>0.0203664743521803</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6952</v>
+        <v>7714</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>412.4494660172727</v>
+        <v>430.1086551716622</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>6.785131509273185</v>
+        <v>46.24493016167287</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>21.78134874937744</v>
+        <v>23.3348851922939</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.0060295447693699</v>
+        <v>0.6152613801573152</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-2.47944552526845</v>
+        <v>-1.320717953998337</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6944</v>
+        <v>6952</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>406.6981064651711</v>
+        <v>412.4494660172727</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>695</v>
+        <v>0</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>35.88661272004538</v>
+        <v>6.785131509273185</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>26.44802706772053</v>
+        <v>21.78134874937744</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.728119725326747</v>
+        <v>0.0060295447693699</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>4.864830176597799</v>
+        <v>-2.47944552526845</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6958</v>
+        <v>6944</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>402.0888722113538</v>
+        <v>406.6981064651711</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>17.2</v>
+        <v>695</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>43.46179312832165</v>
+        <v>35.88661272004538</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.11996797953859</v>
+        <v>26.44802706772053</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6913607888135538</v>
+        <v>1.728119725326747</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.06398402224079131</v>
+        <v>4.864830176597799</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6854</v>
+        <v>6958</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>396.5993568816217</v>
+        <v>402.0888722113538</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>92.7</v>
+        <v>17.2</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45.43776141304542</v>
+        <v>43.46179312832165</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.6787161914481</v>
+        <v>15.11996797953859</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>3.002741413427248</v>
+        <v>0.6913607888135538</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.280003910976815</v>
+        <v>-0.06398402224079131</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7780</v>
+        <v>6854</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>394.4060463426621</v>
+        <v>396.5993568816217</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>16.65</v>
+        <v>92.7</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>42.78708610034072</v>
+        <v>45.43776141304542</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.89342610742246</v>
+        <v>21.6787161914481</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.897207269257056</v>
+        <v>3.002741413427248</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0355067432959533</v>
+        <v>1.280003910976815</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7689</v>
+        <v>7780</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>390.483551366348</v>
+        <v>394.4060463426621</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>170.5</v>
+        <v>16.65</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>33.80777894107136</v>
+        <v>42.78708610034072</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>21.46512942767617</v>
+        <v>17.89342610742246</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4420905056458596</v>
+        <v>1.897207269257056</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.663274772158803</v>
+        <v>0.0355067432959533</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6887</v>
+        <v>7689</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>389.953171846802</v>
+        <v>390.483551366348</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>37.15</v>
+        <v>170.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>50.41465682768579</v>
+        <v>33.80777894107136</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>27.52569284373044</v>
+        <v>21.46512942767617</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.2070430882547043</v>
+        <v>0.4420905056458596</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.0067219482079193</v>
+        <v>1.663274772158803</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3071,21 +3071,21 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6865</v>
+        <v>6887</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>389.5834953189653</v>
+        <v>389.953171846802</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>25.1</v>
+        <v>37.15</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.64581362224012</v>
+        <v>50.41465682768579</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>10.26131336682115</v>
+        <v>27.52569284373044</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.860324828358324</v>
+        <v>0.2070430882547043</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.7805259543127281</v>
+        <v>0.0067219482079193</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6894</v>
+        <v>6865</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>386.2265315672385</v>
+        <v>389.5834953189653</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>349</v>
+        <v>25.1</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>55.40465992921856</v>
+        <v>52.64581362224012</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15.99202817600991</v>
+        <v>10.26131336682115</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6349940252900278</v>
+        <v>1.860324828358324</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>2.803692120088645</v>
+        <v>0.7805259543127281</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8028</v>
+        <v>6894</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>385.4086909385749</v>
+        <v>386.2265315672385</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>236.5</v>
+        <v>349</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>39.42495860490561</v>
+        <v>55.40465992921856</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>21.26537277404944</v>
+        <v>15.99202817600991</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6765188897371339</v>
+        <v>0.6349940252900278</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.8565491498156472</v>
+        <v>2.803692120088645</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>7842</v>
+        <v>8028</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>382.0013025543485</v>
+        <v>385.4086909385749</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>236.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>53.01904208305896</v>
+        <v>39.42495860490561</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>17.07219114999569</v>
+        <v>21.26537277404944</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2142605280097746</v>
+        <v>0.6765188897371339</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.1201592582704762</v>
+        <v>0.8565491498156472</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>7855</v>
+        <v>7842</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>377.487492348317</v>
+        <v>382.0013025543485</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>42.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>17.84940364329407</v>
+        <v>53.01904208305896</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>49.86788951083365</v>
+        <v>17.07219114999569</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2661775743761022</v>
+        <v>0.2142605280097746</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>1.462445410603991</v>
+        <v>-0.1201592582704762</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7768</v>
+        <v>7855</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>373.1269337525416</v>
+        <v>377.487492348317</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>278</v>
+        <v>42.8</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45.63047027042251</v>
+        <v>17.84940364329407</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>21.47725636239554</v>
+        <v>49.86788951083365</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7197492554435782</v>
+        <v>0.2661775743761022</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.79174103505054</v>
+        <v>1.462445410603991</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7823</v>
+        <v>7768</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>361.9117346533321</v>
+        <v>373.1269337525416</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>83.7</v>
+        <v>278</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>51.11132918728528</v>
+        <v>45.63047027042251</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.70597836472178</v>
+        <v>21.47725636239554</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.991258904714024</v>
+        <v>0.7197492554435782</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0298777867606103</v>
+        <v>1.79174103505054</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3442,21 +3442,21 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7795</v>
+        <v>7823</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>359.0093474247554</v>
+        <v>361.9117346533321</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>489</v>
+        <v>83.7</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>46.53483833674568</v>
+        <v>51.11132918728528</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>21.05773062827377</v>
+        <v>21.70597836472178</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4735951129049625</v>
+        <v>0.991258904714024</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-7.334471903682033</v>
+        <v>-0.0298777867606103</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6924</v>
+        <v>7795</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>357.1718478339312</v>
+        <v>359.0093474247554</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>113.5</v>
+        <v>489</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.78608502392877</v>
+        <v>46.53483833674568</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>18.76063235820307</v>
+        <v>21.05773062827377</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3955533233885295</v>
+        <v>0.4735951129049625</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0761344229316599</v>
+        <v>-7.334471903682033</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6962</v>
+        <v>6924</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>355.2795461777366</v>
+        <v>357.1718478339312</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>31.8</v>
+        <v>113.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>48.21646031746988</v>
+        <v>49.78608502392877</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>16.8028471423872</v>
+        <v>18.76063235820307</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6294224575055012</v>
+        <v>0.3955533233885295</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.2183034992001319</v>
+        <v>0.0761344229316599</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6951</v>
+        <v>6962</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>342.2994285079959</v>
+        <v>355.2795461777366</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>71.8</v>
+        <v>31.8</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46.43196087936799</v>
+        <v>48.21646031746988</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>23.69979640915714</v>
+        <v>16.8028471423872</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.9191398944719628</v>
+        <v>0.6294224575055012</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1606053477069187</v>
+        <v>0.2183034992001319</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8034</v>
+        <v>6951</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>334.6374191702399</v>
+        <v>342.2994285079959</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>19.5</v>
+        <v>71.8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.47171960960049</v>
+        <v>46.43196087936799</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>27.71756084580592</v>
+        <v>23.69979640915714</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5259229997340894</v>
+        <v>0.9191398944719628</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1888870929232223</v>
+        <v>0.1606053477069187</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7805</v>
+        <v>8034</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>334.4240415245615</v>
+        <v>334.6374191702399</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>502</v>
+        <v>19.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>28.83888138155585</v>
+        <v>50.47171960960049</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>37.44661439779132</v>
+        <v>27.71756084580592</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6715495006943986</v>
+        <v>0.5259229997340894</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-12.4667091305795</v>
+        <v>0.1888870929232223</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6910</v>
+        <v>7805</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>334.0191097145554</v>
+        <v>334.4240415245615</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>24.8</v>
+        <v>502</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.92356433368037</v>
+        <v>28.83888138155585</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>20.16959964979185</v>
+        <v>37.44661439779132</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8379685475584148</v>
+        <v>0.6715495006943986</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1281568683125786</v>
+        <v>-12.4667091305795</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8033</v>
+        <v>6910</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>324.7152072344085</v>
+        <v>334.0191097145554</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>173</v>
+        <v>24.8</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>43.57908958771326</v>
+        <v>48.92356433368037</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.92199300887676</v>
+        <v>20.16959964979185</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6061391576213999</v>
+        <v>0.8379685475584148</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.151070270796785</v>
+        <v>0.1281568683125786</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>7717</v>
+        <v>8033</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>323.9594669882537</v>
+        <v>324.7152072344085</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>409</v>
+        <v>173</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45.9394963256331</v>
+        <v>43.57908958771326</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>13.11556988310109</v>
+        <v>12.92199300887676</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.912512646655366</v>
+        <v>0.6061391576213999</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>3.219149557159515</v>
+        <v>-1.151070270796785</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>7791</v>
+        <v>7717</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>320.2300632361598</v>
+        <v>323.9594669882537</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>55.3</v>
+        <v>409</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>22.24743398719203</v>
+        <v>45.9394963256331</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>38.17746866459874</v>
+        <v>13.11556988310109</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.025005143619766</v>
+        <v>0.912512646655366</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0019668527552076</v>
+        <v>3.219149557159515</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6997</v>
+        <v>7791</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>319.7235965687344</v>
+        <v>320.2300632361598</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>68</v>
+        <v>55.3</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.26043999609202</v>
+        <v>22.24743398719203</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>7.656396784892181</v>
+        <v>38.17746866459874</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.29964055259625</v>
+        <v>1.025005143619766</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>1.558890947505641</v>
+        <v>0.0019668527552076</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6994</v>
+        <v>6997</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>315.9282792423552</v>
+        <v>319.7235965687344</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>35.55</v>
+        <v>68</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>39.60832847116312</v>
+        <v>52.26043999609202</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>28.0421037391906</v>
+        <v>7.656396784892181</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7286696147445652</v>
+        <v>1.29964055259625</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.3573570335760285</v>
+        <v>1.558890947505641</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7765</v>
+        <v>6994</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>314.7359688898538</v>
+        <v>315.9282792423552</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>222</v>
+        <v>35.55</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>42.47622656879267</v>
+        <v>39.60832847116312</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>23.9627112588249</v>
+        <v>28.0421037391906</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.343717997840399</v>
+        <v>0.7286696147445652</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0671176533866875</v>
+        <v>0.3573570335760285</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6931</v>
+        <v>7765</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>314.3551799498799</v>
+        <v>314.7359688898538</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>40.95</v>
+        <v>222</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.06158796903373</v>
+        <v>42.47622656879267</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>27.16069452726456</v>
+        <v>23.9627112588249</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.2625271581892071</v>
+        <v>1.343717997840399</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.07319438942575381</v>
+        <v>-0.0671176533866875</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6934</v>
+        <v>6931</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>311.4374776713875</v>
+        <v>314.3551799498799</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>74</v>
+        <v>40.95</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.3049727683828</v>
+        <v>52.06158796903373</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>14.30203845840711</v>
+        <v>27.16069452726456</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.833273377274012</v>
+        <v>0.2625271581892071</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.2761289446449945</v>
+        <v>-0.07319438942575381</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6914</v>
+        <v>6934</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>309.0045765887629</v>
+        <v>311.4374776713875</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>20.73961393625886</v>
+        <v>50.3049727683828</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>31.89951789706859</v>
+        <v>14.30203845840711</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.169526543841946</v>
+        <v>1.833273377274012</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-2.585868900306003</v>
+        <v>0.2761289446449945</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7704</v>
+        <v>6914</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>308.8854293245288</v>
+        <v>309.0045765887629</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>60.1</v>
+        <v>122</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>43.92951502362686</v>
+        <v>20.73961393625886</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>16.58342505742802</v>
+        <v>31.89951789706859</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2.037702827712078</v>
+        <v>0.169526543841946</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.4329819604349357</v>
+        <v>-2.585868900306003</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8040</v>
+        <v>7704</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>307.9154029085273</v>
+        <v>308.8854293245288</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>74.7</v>
+        <v>60.1</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>50.33930155881807</v>
+        <v>43.92951502362686</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18.57786010160617</v>
+        <v>16.58342505742802</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>8.177663574987928</v>
+        <v>2.037702827712078</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>1.34232951919093</v>
+        <v>-0.4329819604349357</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6957</v>
+        <v>8040</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>305.2401452839718</v>
+        <v>307.9154029085273</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>217.5</v>
+        <v>74.7</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.18398170332464</v>
+        <v>50.33930155881807</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>14.2170816824115</v>
+        <v>18.57786010160617</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4755068060490585</v>
+        <v>8.177663574987928</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0454811082896607</v>
+        <v>1.34232951919093</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7736</v>
+        <v>6957</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>302.4686053644483</v>
+        <v>305.2401452839718</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>217.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.21610664613036</v>
+        <v>49.18398170332464</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>14.15982726062249</v>
+        <v>14.2170816824115</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.079808878365541</v>
+        <v>0.4755068060490585</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0109356670022383</v>
+        <v>-0.0454811082896607</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6965</v>
+        <v>7736</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>296.6135245458571</v>
+        <v>302.4686053644483</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>73.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>38.68148208041444</v>
+        <v>50.21610664613036</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>36.95191761862112</v>
+        <v>14.15982726062249</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.6303172037871496</v>
+        <v>1.079808878365541</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0154248946297206</v>
+        <v>0.0109356670022383</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6863</v>
+        <v>6965</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>295.9070139825552</v>
+        <v>296.6135245458571</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>104</v>
+        <v>73.7</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>36.23024541304378</v>
+        <v>38.68148208041444</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.45866082876221</v>
+        <v>36.95191761862112</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5718938787624347</v>
+        <v>0.6303172037871496</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-1.236720304636261</v>
+        <v>-0.0154248946297206</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8024</v>
+        <v>6863</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>293.9265629923865</v>
+        <v>295.9070139825552</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>12.9</v>
+        <v>104</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>34.82052004424501</v>
+        <v>36.23024541304378</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.30334865731247</v>
+        <v>16.45866082876221</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.308475164318344</v>
+        <v>0.5718938787624347</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0108050638675849</v>
+        <v>-1.236720304636261</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4661,21 +4661,21 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6903</v>
+        <v>8024</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>293.8058624559833</v>
+        <v>293.9265629923865</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>305.5</v>
+        <v>12.9</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>41.04946158135068</v>
+        <v>34.82052004424501</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>14.25331463691509</v>
+        <v>14.30334865731247</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7342128944127867</v>
+        <v>1.308475164318344</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>1.597745624935051</v>
+        <v>0.0108050638675849</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6967</v>
+        <v>6903</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>291.8246782392893</v>
+        <v>293.8058624559833</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>69.3</v>
+        <v>305.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.07883585415277</v>
+        <v>41.04946158135068</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>8.491423508910557</v>
+        <v>14.25331463691509</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.354554576759244</v>
+        <v>0.7342128944127867</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.2154727199913801</v>
+        <v>1.597745624935051</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7747</v>
+        <v>6967</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>288.7597074223023</v>
+        <v>291.8246782392893</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>113</v>
+        <v>69.3</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>51.94259221198568</v>
+        <v>42.07883585415277</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>8.005920135054513</v>
+        <v>8.491423508910557</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.167173887438782</v>
+        <v>1.354554576759244</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>1.87533168191706</v>
+        <v>-0.2154727199913801</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>7822</v>
+        <v>7747</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>285.9810637994166</v>
+        <v>288.7597074223023</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>898</v>
+        <v>113</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>47.47688515420325</v>
+        <v>51.94259221198568</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>11.57509849105259</v>
+        <v>8.005920135054513</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6335182093219354</v>
+        <v>0.167173887438782</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>4.692580362305532</v>
+        <v>1.87533168191706</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6890</v>
+        <v>7822</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>283.783343683813</v>
+        <v>285.9810637994166</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>169</v>
+        <v>898</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>48.234531927044</v>
+        <v>47.47688515420325</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.78176501651856</v>
+        <v>11.57509849105259</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.132543420811652</v>
+        <v>0.6335182093219354</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>1.257862407538495</v>
+        <v>4.692580362305532</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7828</v>
+        <v>6890</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>282.458155092005</v>
+        <v>283.783343683813</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1755</v>
+        <v>169</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>52.93423587116657</v>
+        <v>48.234531927044</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13.44731521573722</v>
+        <v>13.78176501651856</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.118355420928527</v>
+        <v>1.132543420811652</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>23.09108379484308</v>
+        <v>1.257862407538495</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>7734</v>
+        <v>7828</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>281.7640300340096</v>
+        <v>282.458155092005</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>2710</v>
+        <v>1755</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>40.27169320836045</v>
+        <v>52.93423587116657</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.65818939505464</v>
+        <v>13.44731521573722</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.7634274118402253</v>
+        <v>1.118355420928527</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-24.10965799174059</v>
+        <v>23.09108379484308</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8016</v>
+        <v>7734</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>273.6334038940094</v>
+        <v>281.7640300340096</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>290</v>
+        <v>2710</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>46.09659198689903</v>
+        <v>40.27169320836045</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>9.193659856143404</v>
+        <v>16.65818939505464</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5598948474858823</v>
+        <v>0.7634274118402253</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.4500822022705313</v>
+        <v>-24.10965799174059</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5085,21 +5085,21 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>7751</v>
+        <v>8016</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>271.5900729839372</v>
+        <v>273.6334038940094</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>1465</v>
+        <v>290</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>47.11305542693639</v>
+        <v>46.09659198689903</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>18.62822200964533</v>
+        <v>9.193659856143404</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.8036692084193123</v>
+        <v>0.5598948474858823</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-18.85357119920215</v>
+        <v>-0.4500822022705313</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6855</v>
+        <v>7751</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>271.3519029603838</v>
+        <v>271.5900729839372</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>0</v>
+        <v>1465</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.62147252985026</v>
+        <v>47.11305542693639</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>10.59564537049793</v>
+        <v>18.62822200964533</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.0157550022132026</v>
+        <v>0.8036692084193123</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-3.293683106781808</v>
+        <v>-18.85357119920215</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7827</v>
+        <v>6855</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>271.2764468453387</v>
+        <v>271.3519029603838</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>151.5</v>
+        <v>0</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>42.66346731815072</v>
+        <v>44.62147252985026</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>9.968654045547936</v>
+        <v>10.59564537049793</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5172900157317832</v>
+        <v>0.0157550022132026</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.8778952529534474</v>
+        <v>-3.293683106781808</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7721</v>
+        <v>7827</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>256.1882951643739</v>
+        <v>271.2764468453387</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>60.3</v>
+        <v>151.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>40.12065139439387</v>
+        <v>42.66346731815072</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>15.31300755142944</v>
+        <v>9.968654045547936</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>2.286415857814087</v>
+        <v>0.5172900157317832</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.1087807415469566</v>
+        <v>-0.8778952529534474</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6971</v>
+        <v>7721</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>242.202100259114</v>
+        <v>256.1882951643739</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>26.05</v>
+        <v>60.3</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>47.54759312818067</v>
+        <v>40.12065139439387</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16.03467409982381</v>
+        <v>15.31300755142944</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.697943783758988</v>
+        <v>2.286415857814087</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.062063202490248</v>
+        <v>0.1087807415469566</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>7715</v>
+        <v>6971</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>240.1557862154444</v>
+        <v>242.202100259114</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>28.9</v>
+        <v>26.05</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>36.26276270426627</v>
+        <v>47.54759312818067</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>20.70462483294778</v>
+        <v>16.03467409982381</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3620789027261505</v>
+        <v>0.697943783758988</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.2457839331838683</v>
+        <v>0.062063202490248</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6923</v>
+        <v>7715</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>232.7839516102716</v>
+        <v>240.1557862154444</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>75.40000000000001</v>
+        <v>28.9</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>44.81858137330845</v>
+        <v>36.26276270426627</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>8.104995728189643</v>
+        <v>20.70462483294778</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5719366892704647</v>
+        <v>0.3620789027261505</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0798864249356596</v>
+        <v>-0.2457839331838683</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6899</v>
+        <v>6923</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>231.4853378540126</v>
+        <v>232.7839516102716</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>49.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>36.93108729740708</v>
+        <v>44.81858137330845</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>20.71858257833468</v>
+        <v>8.104995728189643</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.7349256722899615</v>
+        <v>0.5719366892704647</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1343171897084993</v>
+        <v>-0.0798864249356596</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6908</v>
+        <v>6899</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>230.1530114051938</v>
+        <v>231.4853378540126</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>30.1</v>
+        <v>49.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>32.04584246982694</v>
+        <v>36.93108729740708</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>33.73218353085381</v>
+        <v>20.71858257833468</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.4754285103440443</v>
+        <v>0.7349256722899615</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.065453123021796</v>
+        <v>0.1343171897084993</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5562,21 +5562,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6862</v>
+        <v>6908</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>228.8781579391753</v>
+        <v>230.1530114051938</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>139</v>
+        <v>30.1</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.64083313114664</v>
+        <v>32.04584246982694</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>14.07710808945442</v>
+        <v>33.73218353085381</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.7508287159667769</v>
+        <v>0.4754285103440443</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>1.166537566829541</v>
+        <v>0.065453123021796</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6955</v>
+        <v>6862</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>228.2129242460192</v>
+        <v>228.8781579391753</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>139</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>46.16819873195888</v>
+        <v>43.64083313114664</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>6.681541859409255</v>
+        <v>14.07710808945442</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4403904060950032</v>
+        <v>0.7508287159667769</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-1.439571637403795</v>
+        <v>1.166537566829541</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7839</v>
+        <v>6955</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>226.5639939797801</v>
+        <v>228.2129242460192</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>44.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.43217926453683</v>
+        <v>46.16819873195888</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>33.36504954170137</v>
+        <v>6.681541859409255</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.2932441267616783</v>
+        <v>0.4403904060950032</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0500466554810412</v>
+        <v>-1.439571637403795</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6916</v>
+        <v>7839</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>226.2134870336112</v>
+        <v>226.5639939797801</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>18.5</v>
+        <v>44.3</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>47.11097565869984</v>
+        <v>41.43217926453683</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>8.678105754705717</v>
+        <v>33.36504954170137</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.313331281758022</v>
+        <v>0.2932441267616783</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0267140377281569</v>
+        <v>-0.0500466554810412</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6928</v>
+        <v>6916</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>225.4579965289764</v>
+        <v>226.2134870336112</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>47.95</v>
+        <v>18.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>47.0922763270388</v>
+        <v>47.11097565869984</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>13.25326581275578</v>
+        <v>8.678105754705717</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.4092507390253777</v>
+        <v>1.313331281758022</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.10672423193267</v>
+        <v>0.0267140377281569</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>7820</v>
+        <v>6928</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>224.8870377272281</v>
+        <v>225.4579965289764</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>118</v>
+        <v>47.95</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>51.04015029896829</v>
+        <v>47.0922763270388</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>17.70232682033645</v>
+        <v>13.25326581275578</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.5714757112216278</v>
+        <v>0.4092507390253777</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.2442054375980573</v>
+        <v>0.10672423193267</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7705</v>
+        <v>7820</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>221</v>
+        <v>224.8870377272281</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>29.8</v>
+        <v>118</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>39.38755572202524</v>
+        <v>51.04015029896829</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.10611165286438</v>
+        <v>17.70232682033645</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>5.710329663730754</v>
+        <v>0.5714757112216278</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.08115943007438579</v>
+        <v>-0.2442054375980573</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6902</v>
+        <v>7705</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>220.1352190087644</v>
+        <v>221</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>124</v>
+        <v>29.8</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>44.60555600456832</v>
+        <v>39.38755572202524</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>11.91104080980613</v>
+        <v>17.10611165286438</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5571450191336182</v>
+        <v>5.710329663730754</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.4232250792885735</v>
+        <v>-0.08115943007438579</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7749</v>
+        <v>6902</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>208.803695771607</v>
+        <v>220.1352190087644</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>363.5</v>
+        <v>124</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>49.79570929186087</v>
+        <v>44.60555600456832</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>17.62963889520484</v>
+        <v>11.91104080980613</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.6417581935044762</v>
+        <v>0.5571450191336182</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>3.301599583849316</v>
+        <v>-0.4232250792885735</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8011</v>
+        <v>7749</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>201.4848461227729</v>
+        <v>208.803695771607</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>15.75</v>
+        <v>363.5</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>40.21736890779695</v>
+        <v>49.79570929186087</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>26.94991620670754</v>
+        <v>17.62963889520484</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.02916974333225</v>
+        <v>0.6417581935044762</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0223511964655952</v>
+        <v>3.301599583849316</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7547</v>
+        <v>8011</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>201.0424429832957</v>
+        <v>201.4848461227729</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>50.6</v>
+        <v>15.75</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>44.09932078587951</v>
+        <v>40.21736890779695</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>11.94577053192828</v>
+        <v>26.94991620670754</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.1378535147344199</v>
+        <v>1.02916974333225</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0596203937706514</v>
+        <v>0.0223511964655952</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6901</v>
+        <v>7547</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>194.2196332270778</v>
+        <v>201.0424429832957</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>14.9</v>
+        <v>50.6</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>36.10328077384902</v>
+        <v>44.09932078587951</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11.82945983451758</v>
+        <v>11.94577053192828</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4777314209887309</v>
+        <v>0.1378535147344199</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.1657261900731247</v>
+        <v>-0.0596203937706514</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>7799</v>
+        <v>6901</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>193.4765001663045</v>
+        <v>194.2196332270778</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>352</v>
+        <v>14.9</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>43.85117536022301</v>
+        <v>36.10328077384902</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.94651221078794</v>
+        <v>11.82945983451758</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.8678915770643268</v>
+        <v>0.4777314209887309</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.7758607131335769</v>
+        <v>-0.1657261900731247</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6873</v>
+        <v>7799</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>186.9111302499306</v>
+        <v>193.4765001663045</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>352</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>34.92685364123064</v>
+        <v>43.85117536022301</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>24.12989320704521</v>
+        <v>13.94651221078794</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.3701223697869743</v>
+        <v>0.8678915770643268</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.3520371823857222</v>
+        <v>0.7758607131335769</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8032</v>
+        <v>6873</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>183.1370078047778</v>
+        <v>186.9111302499305</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>35.4</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>39.37181387351352</v>
+        <v>34.92685364123064</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>19.42890015129316</v>
+        <v>24.12989320704521</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.9408204175529919</v>
+        <v>0.3701223697869743</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1044659588085856</v>
+        <v>0.3520371823857222</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>7732</v>
+        <v>8032</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>182.7761397844497</v>
+        <v>183.1370078047778</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>33.5</v>
+        <v>35.4</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>45.00452125935465</v>
+        <v>39.37181387351352</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>5.996977714672795</v>
+        <v>19.42890015129316</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.1346434137491122</v>
+        <v>0.9408204175529919</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1339324165064301</v>
+        <v>0.1044659588085856</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8038</v>
+        <v>7732</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>169.455103247597</v>
+        <v>182.7761397844497</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>30.85</v>
+        <v>33.5</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>38.17930561108741</v>
+        <v>45.00452125935465</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>20.59001295257804</v>
+        <v>5.996977714672795</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.167131172458074</v>
+        <v>0.1346434137491122</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.2945292071966312</v>
+        <v>-0.1339324165064301</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6919</v>
+        <v>8038</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>166.7646238123856</v>
+        <v>169.455103247597</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>84.5</v>
+        <v>30.85</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>29.82909387962407</v>
+        <v>38.17930561108741</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>18.64722607396448</v>
+        <v>20.59001295257804</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.076462381238562</v>
+        <v>1.167131172458074</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-2.524265053572736</v>
+        <v>0.2945292071966312</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6988</v>
+        <v>6919</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>166.6822375014095</v>
+        <v>166.7646238123856</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>11.3</v>
+        <v>84.5</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>43.49928670548172</v>
+        <v>29.82909387962407</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>6.863435068076558</v>
+        <v>18.64722607396448</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.9078826381342472</v>
+        <v>1.076462381238562</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0400584385120323</v>
+        <v>-2.524265053572736</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>7760</v>
+        <v>6988</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>163.4677256761706</v>
+        <v>166.6822375014095</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>33.2</v>
+        <v>11.3</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>48.27195124608314</v>
+        <v>43.49928670548172</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>7.41852092778313</v>
+        <v>6.863435068076558</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.13480374266254</v>
+        <v>0.9078826381342472</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0535142743353637</v>
+        <v>-0.0400584385120323</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7722</v>
+        <v>7760</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>162.4856073052817</v>
+        <v>163.4677256761706</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>274.5</v>
+        <v>33.2</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>42.44239585587045</v>
+        <v>48.27195124608314</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>11.21198841908358</v>
+        <v>7.41852092778313</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5434819848714771</v>
+        <v>1.13480374266254</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.1318746085583684</v>
+        <v>0.0535142743353637</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7821</v>
+        <v>7722</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>156.0155928134491</v>
+        <v>162.4856073052817</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>39.4</v>
+        <v>274.5</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>46.47008742885905</v>
+        <v>42.44239585587045</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>12.3436438900209</v>
+        <v>11.21198841908358</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.140411354481006</v>
+        <v>0.5434819848714771</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.1219576375494081</v>
+        <v>0.1318746085583684</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6728,21 +6728,21 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6947</v>
+        <v>7821</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>154.9076200798922</v>
+        <v>156.0155928134491</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>68.40000000000001</v>
+        <v>39.4</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>33.70252579510952</v>
+        <v>46.47008742885905</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>11.77787151870221</v>
+        <v>12.3436438900209</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.037426789866853</v>
+        <v>1.140411354481006</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.0787221027211311</v>
+        <v>0.1219576375494081</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7803</v>
+        <v>6947</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>151.9575053468421</v>
+        <v>154.9076200798922</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>19.1</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>39.36577223695673</v>
+        <v>33.70252579510952</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>11.72710972427004</v>
+        <v>11.77787151870221</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.3994476285268885</v>
+        <v>1.037426789866853</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.07552709150296411</v>
+        <v>0.0787221027211311</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>7770</v>
+        <v>7803</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>150.086189475653</v>
+        <v>151.9575053468421</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>35.75</v>
+        <v>19.1</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>48.58491161217606</v>
+        <v>39.36577223695673</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>5.621652629886494</v>
+        <v>11.72710972427004</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.8727818045488628</v>
+        <v>0.3994476285268885</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0734119614757258</v>
+        <v>0.07552709150296411</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>7786</v>
+        <v>7770</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>148.2278585561866</v>
+        <v>150.086189475653</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>116.5</v>
+        <v>35.75</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>35.81492151772019</v>
+        <v>48.58491161217606</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>15.04878070450943</v>
+        <v>5.621652629886494</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.2733183000335896</v>
+        <v>0.8727818045488628</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.6308432578218865</v>
+        <v>-0.0734119614757258</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7740</v>
+        <v>7786</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>142.6176291238416</v>
+        <v>148.2278585561866</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>129</v>
+        <v>116.5</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>36.76520086345469</v>
+        <v>35.81492151772019</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>14.09083618930184</v>
+        <v>15.04878070450943</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.3485250978512882</v>
+        <v>0.2733183000335896</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.8963006013910562</v>
+        <v>-0.6308432578218865</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6921</v>
+        <v>7740</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>140.1161612469308</v>
+        <v>142.6176291238416</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>63.7</v>
+        <v>129</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>42.70961247663033</v>
+        <v>36.76520086345469</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>18.64107111583141</v>
+        <v>14.09083618930184</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.1475276683445406</v>
+        <v>0.3485250978512882</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.5582285275123303</v>
+        <v>-0.8963006013910562</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,21 +7046,21 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6909</v>
+        <v>6921</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>118.8700462697703</v>
+        <v>140.1161612469308</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>39.6</v>
+        <v>63.7</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>39.7758863395884</v>
+        <v>42.70961247663033</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>16.04811491587347</v>
+        <v>18.64107111583141</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.247533414018102</v>
+        <v>0.1475276683445406</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.2996038988642848</v>
+        <v>-0.5582285275123303</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7099,21 +7099,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>7753</v>
+        <v>6909</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>106.4908273449698</v>
+        <v>118.8700462697703</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>36.3</v>
+        <v>39.6</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>35.50647027592879</v>
+        <v>39.7758863395884</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>9.340130264656588</v>
+        <v>16.04811491587347</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.296952552664574</v>
+        <v>1.247533414018102</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.0126360625280811</v>
+        <v>0.2996038988642848</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>6925</v>
+        <v>7753</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>102.2368108357844</v>
+        <v>106.4908273449698</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>50</v>
+        <v>36.3</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>39.42291086363767</v>
+        <v>35.50647027592879</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>11.05811652532619</v>
+        <v>9.340130264656588</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.3400824484813906</v>
+        <v>1.296952552664574</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.1913536954241472</v>
+        <v>0.0126360625280811</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7205,52 +7205,105 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
+        <v>6925</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>意藍</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>102.2368108357844</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>39.42291086363767</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>11.05811652532619</v>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>0.3400824484813906</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" s="2" t="n">
+        <v>0.1913536954241472</v>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
         <v>6869</v>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>雲豹能源</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D128" s="2" t="n">
+      <c r="C129" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D129" s="2" t="n">
         <v>97.14962488788302</v>
       </c>
-      <c r="E128" s="2" t="n">
+      <c r="E129" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H128" s="2" t="n">
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H129" s="2" t="n">
         <v>42.58901210145181</v>
       </c>
-      <c r="I128" s="2" t="n">
+      <c r="I129" s="2" t="n">
         <v>14.57714020005343</v>
       </c>
-      <c r="J128" s="2" t="n">
+      <c r="J129" s="2" t="n">
         <v>0.6725419858018508</v>
       </c>
-      <c r="K128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N128" s="2" t="n">
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" s="2" t="n">
         <v>0.0635507525386963</v>
       </c>
-      <c r="O128" s="2" t="inlineStr">
+      <c r="O129" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
